--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.70279214549592</v>
+        <v>11.65170372364309</v>
       </c>
       <c r="D2" t="n">
-        <v>54.88680466753924</v>
+        <v>8.919105758475126</v>
       </c>
       <c r="E2" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F2" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.77378927525096</v>
+        <v>5.650740757228282</v>
       </c>
       <c r="D3" t="n">
-        <v>35.0719038666487</v>
+        <v>5.699184378330415</v>
       </c>
       <c r="E3" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F3" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.59434666731026</v>
+        <v>7.409081333437918</v>
       </c>
       <c r="D4" t="n">
-        <v>29.70443389201533</v>
+        <v>4.826970507452492</v>
       </c>
       <c r="E4" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F4" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.36955016871611</v>
+        <v>5.910051902416368</v>
       </c>
       <c r="D5" t="n">
-        <v>20.88512081853821</v>
+        <v>3.393832133012459</v>
       </c>
       <c r="E5" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F5" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.82359223650657</v>
+        <v>6.308833738432318</v>
       </c>
       <c r="D6" t="n">
-        <v>23.42493994774705</v>
+        <v>3.806552741508896</v>
       </c>
       <c r="E6" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F6" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.86421484078409</v>
+        <v>7.615434911627414</v>
       </c>
       <c r="D7" t="n">
-        <v>25.95006208379483</v>
+        <v>4.21688508861666</v>
       </c>
       <c r="E7" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F7" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.151969585332443</v>
+        <v>1.487195057616522</v>
       </c>
       <c r="D8" t="n">
-        <v>13.43893367316042</v>
+        <v>2.183826721888568</v>
       </c>
       <c r="E8" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F8" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.38069111189306</v>
+        <v>4.936862305682623</v>
       </c>
       <c r="D9" t="n">
-        <v>2.099502022320521</v>
+        <v>0.3411690786270847</v>
       </c>
       <c r="E9" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F9" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.63279357844312</v>
+        <v>3.352828956497008</v>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>2.03125</v>
       </c>
       <c r="E10" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F10" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.10161155933764</v>
+        <v>2.129011878392367</v>
       </c>
       <c r="D11" t="n">
-        <v>23.91166049469385</v>
+        <v>3.88564483038775</v>
       </c>
       <c r="E11" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F11" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.92797357597591</v>
+        <v>3.563295706096085</v>
       </c>
       <c r="D12" t="n">
-        <v>20.599770705182</v>
+        <v>3.347462739592075</v>
       </c>
       <c r="E12" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F12" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>4.704202239264068</v>
+        <v>0.764432863880411</v>
       </c>
       <c r="D13" t="n">
-        <v>4.50304496574026</v>
+        <v>0.7317448069327923</v>
       </c>
       <c r="E13" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F13" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.51374681933856</v>
+        <v>3.820983858142516</v>
       </c>
       <c r="D14" t="n">
-        <v>21.89956447841748</v>
+        <v>3.558679227742841</v>
       </c>
       <c r="E14" t="n">
-        <v>17.45046056195647</v>
+        <v>2.835699841317927</v>
       </c>
       <c r="F14" t="n">
-        <v>13.01287952280574</v>
+        <v>2.114592922455932</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
